--- a/Configs/GameConfig/Datas/gameplay_graph_trigger.xlsx
+++ b/Configs/GameConfig/Datas/gameplay_graph_trigger.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24810" windowHeight="11955"/>
+    <workbookView windowWidth="28800" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1067,8 +1067,8 @@
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
     <col min="2" max="2" width="16.125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="26.75" customWidth="1"/>
-    <col min="4" max="5" width="23.875" customWidth="1"/>
+    <col min="3" max="4" width="26.75" customWidth="1"/>
+    <col min="5" max="5" width="23.875" customWidth="1"/>
     <col min="6" max="6" width="23.875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
